--- a/R Markdown/resultados/Produtos_Cesta_2026/tabelas/auditoria_filtragem.xlsx
+++ b/R Markdown/resultados/Produtos_Cesta_2026/tabelas/auditoria_filtragem.xlsx
@@ -1,21 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/Produtos_Cesta_2026/tabelas/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_4E68FDCE8F79A8D366075C52F3D132701A1CF34B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B947A707-0FAC-4A04-923B-20F2DC7747ED}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>valor</t>
+  </si>
+  <si>
+    <t>Registros válidos na base principal</t>
+  </si>
+  <si>
+    <t>Subprefeituras oficiais validadas</t>
+  </si>
+  <si>
+    <t>Registros territoriais inválidos removidos</t>
+  </si>
+  <si>
+    <t>Duplicidades exatas auditadas</t>
+  </si>
+  <si>
+    <t>Ações na cesta oficial</t>
+  </si>
+  <si>
+    <t>Ações após filtro</t>
+  </si>
+  <si>
+    <t>Ações faltantes na base</t>
+  </si>
+  <si>
+    <t>Ações externas ao filtro</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +104,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +156,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +190,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +225,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,69 +401,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ações nos dados brutos</t>
-        </is>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ações na cesta oficial</t>
-        </is>
+        <v>24462</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
       </c>
       <c r="B3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
         <v>87</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ações após filtro</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ações faltantes na base</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Ações externas ao filtro</t>
-        </is>
-      </c>
-      <c r="B6">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
         <v>0</v>
       </c>
     </row>

--- a/R Markdown/resultados/Produtos_Cesta_2026/tabelas/auditoria_filtragem.xlsx
+++ b/R Markdown/resultados/Produtos_Cesta_2026/tabelas/auditoria_filtragem.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,7 +15,23 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -56,7 +72,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,12 +419,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -424,7 +440,7 @@
         <v>24462</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -432,7 +448,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -440,7 +456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -448,7 +464,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -456,7 +472,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -464,7 +480,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -472,7 +488,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>

--- a/R Markdown/resultados/Produtos_Cesta_2026/tabelas/auditoria_filtragem.xlsx
+++ b/R Markdown/resultados/Produtos_Cesta_2026/tabelas/auditoria_filtragem.xlsx
@@ -1,77 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/Produtos_Cesta_2026/tabelas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_4E68FDCE8F79A8D366075C52F3D132701A1CF34B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B947A707-0FAC-4A04-923B-20F2DC7747ED}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>valor</t>
-  </si>
-  <si>
-    <t>Registros válidos na base principal</t>
-  </si>
-  <si>
-    <t>Subprefeituras oficiais validadas</t>
-  </si>
-  <si>
-    <t>Registros territoriais inválidos removidos</t>
-  </si>
-  <si>
-    <t>Duplicidades exatas auditadas</t>
-  </si>
-  <si>
-    <t>Ações na cesta oficial</t>
-  </si>
-  <si>
-    <t>Ações após filtro</t>
-  </si>
-  <si>
-    <t>Ações faltantes na base</t>
-  </si>
-  <si>
-    <t>Ações externas ao filtro</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -120,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -172,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -206,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -241,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -417,80 +350,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Registros válidos na base principal</t>
+        </is>
       </c>
       <c r="B2">
         <v>24462</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Subprefeituras oficiais validadas</t>
+        </is>
       </c>
       <c r="B3">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Registros territoriais inválidos removidos</t>
+        </is>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>5</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Duplicidades exatas auditadas</t>
+        </is>
       </c>
       <c r="B5">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ações na cesta oficial</t>
+        </is>
       </c>
       <c r="B6">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>7</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ações após filtro</t>
+        </is>
       </c>
       <c r="B7">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ações faltantes na base</t>
+        </is>
       </c>
       <c r="B8">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>9</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ações externas ao filtro</t>
+        </is>
       </c>
       <c r="B9">
         <v>0</v>
